--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.714960639075303</v>
+        <v>0.9286811038497368</v>
       </c>
       <c r="D2" t="n">
-        <v>9.892174794147534</v>
+        <v>1.607478404048974</v>
       </c>
       <c r="E2" t="n">
-        <v>14.03092102203857</v>
+        <v>2.280024666081268</v>
       </c>
       <c r="F2" t="n">
-        <v>7.376111892150157</v>
+        <v>1.198618182474401</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.77680268315245</v>
+        <v>5.488730436012274</v>
       </c>
       <c r="D3" t="n">
-        <v>24.64439857844785</v>
+        <v>4.004714768997776</v>
       </c>
       <c r="E3" t="n">
-        <v>14.03092102203857</v>
+        <v>2.280024666081268</v>
       </c>
       <c r="F3" t="n">
-        <v>7.376111892150157</v>
+        <v>1.198618182474401</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
